--- a/Data/PNW_estuaries_metadata.xlsx
+++ b/Data/PNW_estuaries_metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rekha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvic-my.sharepoint.com/personal/rekhamarcus_uvic_ca/Documents/Wetlands/PNW_Estuaries/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D019B7-6419-44B0-966B-C951A0E3261E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{41D019B7-6419-44B0-966B-C951A0E3261E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921D158E-48D8-451D-83BF-54768BD354D9}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="1770" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -195,9 +195,6 @@
     <t>Coastal Pacific Northwest (BC, WA, OR, and CA north of San Francisco Bay)</t>
   </si>
   <si>
-    <t xml:space="preserve">Percent change from historical conditions to projected future time periods was calculated.  </t>
-  </si>
-  <si>
     <t>Gerald Singh and Nancy Shackelford (supervision)</t>
   </si>
   <si>
@@ -458,6 +455,9 @@
   </si>
   <si>
     <t>All original climate data acquired from CHELSA (https://www.chelsa-climate.org/)</t>
+  </si>
+  <si>
+    <t>Percent change from historical conditions to projected future time periods was calculated. See https://github.com/rekhamarcus/PNW_Estuaries for complete scripts on data download, processing, and analysis</t>
   </si>
 </sst>
 </file>
@@ -761,9 +761,48 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -773,7 +812,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -782,49 +824,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1121,113 +1121,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="26"/>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" ht="19.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="14.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="24"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="14.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="24"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="24.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="24"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="14.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="24"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" ht="14.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="37">
         <v>45809</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="24"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" ht="14.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="38">
         <v>46035</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="26"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" ht="19.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10" t="s">
@@ -1311,216 +1311,216 @@
       <c r="A16" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="24"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="24"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" ht="24.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="24"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" ht="23.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="24"/>
+      <c r="B19" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="30"/>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" ht="16.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="24"/>
+      <c r="B20" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="30"/>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" ht="25.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A21" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="26"/>
+      <c r="B21" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="40"/>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" ht="16.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="28"/>
+      <c r="B23" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" ht="31.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="30"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="41"/>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="34"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="23"/>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="34"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="23"/>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" ht="25.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="34"/>
+      <c r="B27" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="23"/>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="24"/>
+      <c r="B28" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A29" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="28"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="32"/>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
       <c r="G30" s="15"/>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A31" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="28"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="32"/>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="35"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
     </row>
     <row r="33" spans="1:9" s="2" customFormat="1" ht="19.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
+      <c r="A33" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
       <c r="G33" s="6"/>
     </row>
     <row r="34" spans="1:9" s="2" customFormat="1" ht="19.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1548,368 +1548,368 @@
     </row>
     <row r="35" spans="1:9" s="2" customFormat="1" ht="46.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9" s="2" customFormat="1" ht="175.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9" s="2" customFormat="1" ht="117" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="G37" s="41" t="s">
-        <v>59</v>
       </c>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9" s="2" customFormat="1" ht="88.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G38" s="3"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9" ht="140.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="1:9" s="2" customFormat="1" ht="58.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9" s="1" customFormat="1" ht="70.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="1:9" ht="81.900000000000006" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="1:9" ht="70.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="1:9" ht="70.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="1:9" ht="81.900000000000006" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="1:9" ht="81.900000000000006" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="1:9" ht="93.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="1:9" ht="93.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="1:7" ht="81.900000000000006" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="1:7" ht="93.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="1:7" ht="93.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G51" s="2"/>
     </row>
@@ -1958,11 +1958,10 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B27:G27"/>
@@ -1970,6 +1969,11 @@
     <mergeCell ref="B29:G29"/>
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="B5:G5"/>
@@ -1981,10 +1985,6 @@
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B24:G24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B14" r:id="rId1" xr:uid="{C80FF7A2-0A5F-4A01-8A53-E95DC1687B9D}"/>
@@ -2005,6 +2005,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100483727557648AA40B029C215891F95C5" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36f379eec1cf084072dcf956aecbcf8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8c008993-a31f-4b40-b1f3-88dd9c6e1924" xmlns:ns4="360018dd-41eb-4458-b1d4-4b46a95a2b02" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd1f472f1ef3281fe4dbeb8213942d38" ns3:_="" ns4:_="">
     <xsd:import namespace="8c008993-a31f-4b40-b1f3-88dd9c6e1924"/>
@@ -2233,12 +2239,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4901A729-BF60-4E35-96E4-F33CC664023D}">
   <ds:schemaRefs>
@@ -2248,6 +2248,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78641E9-6B89-49F8-A64B-E70C791B6886}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8c008993-a31f-4b40-b1f3-88dd9c6e1924"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="360018dd-41eb-4458-b1d4-4b46a95a2b02"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C45E3C36-D906-456C-888F-720E462F2C07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2264,21 +2281,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D78641E9-6B89-49F8-A64B-E70C791B6886}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="8c008993-a31f-4b40-b1f3-88dd9c6e1924"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="360018dd-41eb-4458-b1d4-4b46a95a2b02"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>